--- a/www/download/COUNTRY.LUX.EXI382.xlsx
+++ b/www/download/COUNTRY.LUX.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2439</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.337</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.165</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.174</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.182</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.182</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.182</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.186</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.192</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.195</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.191</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.199</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.216</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.274</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.284</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.284</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0.292</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.308</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>0.317</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.301</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.141</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.147</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.154</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.157</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.168</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.166</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.171</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.177</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.179</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.181</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.186</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.196</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.205</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.233</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.257</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.257</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.278</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>0.285</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>673.38</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>329.4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>333.636</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>336.768</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>332.075</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>345.225</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>355.881</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>367.319</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>367.088</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>357.904</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>360.534</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>367.97</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>376.505</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>381.132</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>370.782</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>392.508</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>388.349</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>402.13</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>430.305</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>450.901</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>517.424</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>543.543</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>561.712</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>563.358</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>577.669</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>609.491</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>628.397</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>595.778</t>
+          <t>470215459.915634</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>229.958</t>
+          <t>691218431.335494</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>248.788</t>
+          <t>651192465.043526</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>255.993</t>
+          <t>750505024.782176</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>245.256</t>
+          <t>926636744.340212</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>261.889</t>
+          <t>993454970.702891</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>265.623</t>
+          <t>961325656.417766</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>294.184</t>
+          <t>976577739.028218</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>291.053</t>
+          <t>942098941.646528</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>277.33</t>
+          <t>1279818925.36748</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>280.268</t>
+          <t>1308657961.4149</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>285.845</t>
+          <t>1266107827.65948</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>298.127</t>
+          <t>1154228877.12392</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>326.732</t>
+          <t>1495977483.70334</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>306.412</t>
+          <t>1350145690.42884</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>312.941</t>
+          <t>1480269989.5475</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>319.241</t>
+          <t>1543148898.98803</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>324.538</t>
+          <t>1606846361.57933</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>341.931</t>
+          <t>1954729950.33548</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>403.663</t>
+          <t>2277575677.92599</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>460.432</t>
+          <t>2727747785.73854</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>488.385</t>
+          <t>3052000334.02677</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>504.299</t>
+          <t>2185916762.12589</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>504.926</t>
+          <t>2708223950.17766</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>516.499</t>
+          <t>2249602543.68073</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>544.936</t>
+          <t>2788604996.49924</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>560.597</t>
+          <t>3244372664.15021</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>271258051.988917</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>466033517.383414</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>632017773.737675</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>912828688.794501</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>934645136.677316</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1306483569.56179</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1856941191.44456</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1609462747.72973</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1137124551.30167</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1277782556.79004</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1629960084.95443</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1833394399.99967</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1519630625.39782</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2099793016.27966</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1927373843.96991</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2140136717.24717</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1718544378.53581</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2442357696.17363</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2619629701.55393</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3092025885.87652</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2926245213.49932</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3042382891.6121</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3188544386.98983</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>4192924705.59033</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3538849511.06103</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3982611469.58869</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4083146058.04676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4300818.3329196</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>19988679.3157104</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8122650.0050066</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8699613.28311533</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8057035.83012287</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7478792.39949166</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6464805.59980326</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5606254.99713371</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6128328.03127446</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7579041.41001889</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7858746.45735765</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6327585.7401914</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6002665.31801139</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6451097.02580251</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7028148.29614141</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6145404.13089529</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5368358.8816339</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6026207.83104007</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6647739.49358881</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>5237163.31568462</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4816235.09495754</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5431754.84153924</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3962506.85640766</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4410378.48328682</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3712804.52092396</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4021434.24310015</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>4889780.54625673</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>968.105380029104</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1253.15576402529</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1319.3780808171</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1370.19686016607</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1378.17445273437</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1733.20211767098</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1701.54287170635</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1707.71838708172</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1576.89302285566</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1529.90131848712</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1572.89712152628</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1713.73417909436</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1893.72748440034</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1892.38209909256</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1864.96348859019</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2078.71798516834</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2121.76325875435</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2422.97904985043</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2575.21251803615</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2720.65434517119</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>3610.15390273475</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3513.64036048121</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3877.72860813911</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3623.46550657563</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>4025.7690255289</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3991.68836870628</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4030.40554720506</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1752.77639047282</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5252.61892441188</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5389.67519707358</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6386.00299174628</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8316.83799605171</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10658.593071021</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10356.1223899027</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10198.0465474157</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>9037.34934688567</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>11997.5624192795</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>13151.7138458428</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13611.0515159267</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>12855.6998336006</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>16742.2462635507</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>15142.0852277816</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>19144.864281185</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>20777.4363392287</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>23879.904754629</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>28376.7741260895</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>34223.3961080491</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>46301.1922729438</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>47218.8332432346</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>35755.2386291188</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>43083.6580182971</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>38130.4723235839</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>44964.7414098325</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>51360.5610823727</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.19634995744402</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.506563387776996</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.606359171627978</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.719560742182638</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.737594526119367</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.799546656305882</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.856956697808272</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.817216024157751</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.744044748953061</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.782959942185625</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.828052231102369</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.844089738683645</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.803816141227113</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.84439799662783</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.841020982536083</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.853775229648638</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.814237558257263</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.867121019779954</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.869473536737949</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.869450242041637</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-0.84265417232166</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-0.839472909542111</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>-0.841840382746588</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-0.879576640469833</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-0.854048996784067</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.863171282804759</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-0.862704754707247</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>901.871915931116</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3307.5480296901</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4317.06129602341</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6114.05685729972</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6375.47842208247</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>8505.75240599982</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11820.1221606861</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9534.73191782965</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6776.66597914899</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>7660.56688722812</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>9836.81403110978</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>10721.6046783637</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>8580.63594239384</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>11633.2023062569</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>10797.6125712569</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>11823.9597637976</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>9494.72032340273</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>13102.7773399871</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>13372.2802529555</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>15097.3888429314</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>12543.0739843224</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>12278.3413464921</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>12409.2461791954</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16344.0782779998</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>13451.3682373675</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14344.8380989307</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>14304.7628340633</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2700906974.04277</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1557774936.9625</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1627087507.54363</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1747944057.88562</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2151344436.65622</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2565313832.43882</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3061810720.32025</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>3166937102.38209</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2822712550.55736</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3297224490.7505</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3476862136.91054</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4100491347.90304</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3433323437.18785</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>4084579593.59591</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>4087780490.15449</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>4122903978.29397</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3944461271.80516</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>4472159562.60976</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>5336711143.84621</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>5372128881.55508</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>5585739391.45537</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>6000848983.57578</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5426012544.08555</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>6215364166.99146</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>5950249845.60207</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6899295129.66193</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>7164979714.37985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1628132780.91907</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1027704601.18351</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1118885374.53873</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1198471580.01258</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1195465319.25035</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1221593014.76362</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1437132744.19638</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1639944358.48964</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1422687494.04095</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1739627605.39565</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1703620812.79988</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1874466767.10444</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1464521146.02632</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1721982794.95243</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1598538855.36746</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1784341599.5052</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1523655237.65631</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1740814380.94187</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2044184702.12771</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1510534266.38389</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1566097195.07371</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>1805043837.3908</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1699838714.4931</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2277507810.58815</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1958478790.16158</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2371334250.18469</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2252171968.0422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1072774193.12371</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>530070335.778992</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>508202133.004898</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>549472477.873039</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>955879117.405867</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1343720817.6752</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1624677976.12387</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1526992743.89246</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1400025056.51642</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1557596885.35485</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1773241324.11066</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2226024580.7986</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1968802291.16153</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2362596798.64348</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2489241634.78703</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2338562378.78876</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2420806034.14886</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2731345181.66789</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3292526441.71849</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3861594615.1712</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>4019642196.38166</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>4195805146.18498</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>3726173829.59246</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3937856356.40331</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>3991771055.44049</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>4527960879.47725</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>4912807746.33765</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1980.82634417526</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1632.06529453515</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1699.37158469945</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1714.62156731428</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1672.9604365623</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1705.00651041696</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>1690.78930617416</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>1742.7962085309</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1734.52324195433</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>1662.64988009488</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1691.41822571024</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1671.60818713434</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1683.38226990415</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>1810.14958448732</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1716.59383753447</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1728.95580110505</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1763.76243093969</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1741.08369098781</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1745.43644716724</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>1970.96045924799</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>1973.60035769387</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1971.00641200118</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1962.64162610492</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>1968.20881466076</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1963.24068887073</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1962.7857954501</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1963.97592215738</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1996.22829636846</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2069.09547738678</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2053.14461538475</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2044.73588342469</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2037.26993865054</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2039.13171884247</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2047.64672036784</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2016.02085620215</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>2013.64783324148</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1970.83700440427</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1991.90055248728</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1975.14761137929</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1958.92299687825</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1956.52977412715</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1937.21003134736</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1968.4453360083</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1970.31456113696</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1967.36790606742</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1988.47042513889</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1989.13107464835</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>1993.81991790748</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1985.94865397591</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1978.42376142941</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1984.85998307458</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1980.32100775001</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1978.48604253794</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1980.30934323612</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5821.52524877739</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10715.6568793241</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12743.0646029694</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>14782.0001317436</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20057.5831717316</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>28187.1327176933</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>29153.0401782218</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>29282.5972613024</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>27207.4998831295</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>28538.3881714544</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>32386.2491559565</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>39865.9951681691</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>40726.3995556885</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>43723.092678254</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>40061.1750772465</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>47411.2791984352</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>49322.9856291096</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>56935.4829152113</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>62244.6628726495</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>80259.7466994237</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>95211.8455321569</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>97443.0161293724</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>104403.956141645</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>107246.972987959</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>114501.113122952</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>123076.59652741</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>127742.747957226</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>78378727.0963412</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>280496565.619566</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>290150461.260197</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>349678006.334018</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>496106258.043594</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>565922625.398153</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>552515400.732922</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>581726504.548647</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>507558267.311503</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>735639252.173887</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>791373427.800909</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>728269035.322745</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>656764841.070463</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>851097936.311423</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>770753230.310399</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>795133709.946511</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>842610902.67118</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>924319580.154949</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1102440995.9253</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1326753155.39494</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>1622186618.10461</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1949760390.97619</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1453388197.37772</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>1859436264.42271</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1474676304.54829</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>1824391902.08762</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2088130334.45674</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1431.41183148486</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5642.11825713682</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7938.19134400709</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10192.1400032008</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>13933.4887917106</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>20653.1285201144</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21841.4605628253</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>21087.2921306714</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>19108.0756215624</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>19469.7664589005</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>22342.4083370984</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>25773.8780509714</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>24568.2815194385</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>28493.4227992003</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>24566.4575703097</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>30146.1073214967</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>30981.5471240593</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>39032.7011096315</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>42777.816307543</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>59166.0749125118</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>72044.9680543111</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>72048.5352251481</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>78273.5296283925</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>78958.6754226529</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>84602.465079548</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>92171.6668675023</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>95787.0626714084</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>673.38</t>
+          <t>292171254.990917</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>329.4</t>
+          <t>807642766.273719</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>333.636</t>
+          <t>1017824712.0876</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>336.768</t>
+          <t>1232900124.5506</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>332.075</t>
+          <t>1524022981.40955</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>345.225</t>
+          <t>1962406689.09989</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>355.881</t>
+          <t>2435121955.9197</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>367.319</t>
+          <t>2377314099.95847</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>367.088</t>
+          <t>1954359600.50759</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>357.904</t>
+          <t>2369770643.07826</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>360.534</t>
+          <t>2588397318.97333</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>367.97</t>
+          <t>2731970326.47886</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>376.505</t>
+          <t>2083534336.10937</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>381.132</t>
+          <t>2848613477.38688</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>370.782</t>
+          <t>2577844403.30956</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>392.508</t>
+          <t>2789207182.58466</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>388.349</t>
+          <t>2672015339.84994</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>402.13</t>
+          <t>3444516794.42177</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>430.305</t>
+          <t>4209155625.9016</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>450.901</t>
+          <t>4456496211.92937</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>517.424</t>
+          <t>4968502499.37055</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>543.543</t>
+          <t>5257358804.48648</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>561.712</t>
+          <t>4362446017.51821</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>563.358</t>
+          <t>5263234848.77598</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>577.669</t>
+          <t>4696154097.4046</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>609.491</t>
+          <t>5724631664.41388</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>628.397</t>
+          <t>6139505488.74214</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>595.778</t>
+          <t>4390.11341729254</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>229.958</t>
+          <t>5073.53862218728</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>248.788</t>
+          <t>4804.87325896233</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>255.993</t>
+          <t>4589.86012854281</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>245.256</t>
+          <t>6124.09438002095</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>261.889</t>
+          <t>7534.00419757884</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>265.623</t>
+          <t>7311.57961539655</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>294.184</t>
+          <t>8195.30513063106</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>291.053</t>
+          <t>8099.42426156716</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>277.33</t>
+          <t>9068.62171255394</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>280.268</t>
+          <t>10043.8408188581</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>285.845</t>
+          <t>14092.1171171977</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>298.127</t>
+          <t>16158.1180362499</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>326.732</t>
+          <t>15229.6698790536</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>306.412</t>
+          <t>15494.7175069368</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>312.941</t>
+          <t>17265.1718769386</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>319.241</t>
+          <t>18341.4385050502</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>324.538</t>
+          <t>17902.7818055798</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>341.931</t>
+          <t>19466.8465651065</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>403.663</t>
+          <t>21093.6717869119</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>460.432</t>
+          <t>23166.8774778458</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>488.385</t>
+          <t>25394.4809042243</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>504.299</t>
+          <t>26130.4265132529</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>504.926</t>
+          <t>28288.2975653064</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>516.499</t>
+          <t>29898.6480434036</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>544.936</t>
+          <t>30904.929659908</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>560.597</t>
+          <t>31955.6852858171</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>412.466</t>
+          <t>-213792527.894576</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>555.552</t>
+          <t>-527146200.654153</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>525.149</t>
+          <t>-727674250.827406</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>604.026</t>
+          <t>-883222118.216586</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>727.919</t>
+          <t>-1027916723.36596</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>778.851</t>
+          <t>-1396484063.70173</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>746.939</t>
+          <t>-1882606555.18678</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>757.805</t>
+          <t>-1795587595.40982</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>744.05</t>
+          <t>-1446801333.19609</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1000.282</t>
+          <t>-1634131390.90437</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1015.232</t>
+          <t>-1797023891.17242</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>983.752</t>
+          <t>-2003701291.15611</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>910.232</t>
+          <t>-1426769495.03891</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1160.074</t>
+          <t>-1997515541.07545</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1048.674</t>
+          <t>-1807091172.99916</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1156.468</t>
+          <t>-1994073472.63815</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1189.708</t>
+          <t>-1829404437.17876</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1233.803</t>
+          <t>-2520197214.26682</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1502.157</t>
+          <t>-3106714629.97631</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1730.063</t>
+          <t>-3129743056.53442</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2056.913</t>
+          <t>-3346315881.26594</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2313.19</t>
+          <t>-3307598413.51029</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1691.888</t>
+          <t>-2909057820.14049</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>2066.424</t>
+          <t>-3403798584.35328</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1738.154</t>
+          <t>-3221477792.85631</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2125.827</t>
+          <t>-3900239762.32626</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2452.319</t>
+          <t>-4051375154.2854</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>5535.76298807727</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5026.29225725614</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5600.48508425105</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5477.68773250702</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5595.22022706655</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6771.34892789429</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7121.03091981875</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7528.5098175079</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8348.00539162095</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7990.16186215604</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8820.80237231796</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9066.6481207659</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10481.2649791109</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11173.8496580922</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10444.4288031861</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>11034.1303353914</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>11259.0854914521</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>11856.3602681147</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>12307.6348757701</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>12777.4672869048</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>13812.4853528948</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>14702.7928686513</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>16528.8822150736</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>17706.725582026</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>17986.6721651891</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>17253.3900843935</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>18082.9136357086</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>259.713</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>164.909</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>159.41</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>161.03</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>153.552</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>161.546</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>157.949</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>163.533</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>164.383</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>163.2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>156.511</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>159.413</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>170.025</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>169.091</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>166.29</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>160.725</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>157.584</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>163.039</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>177.393</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>181.06</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>212.685</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>227.105</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>237.067</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>227.77</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>237.51</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>247.555</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>254.595</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>10991.8880267262</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>10994.3597247422</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>11773.178741773</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>11604.8415952334</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>13340.289840451</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>14135.1146333711</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>15296.9224303501</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>14693.5065690068</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>16297.8804638985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>16226.3499194262</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>18988.6148866997</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>18511.1841541741</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>20310.2125145467</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>23622.6469764836</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>23526.7958564103</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>23828.6817769018</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>24143.3292483383</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>26579.9591415886</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>25562.4367997852</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>29546.7659391252</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>28682.0466310782</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>29908.7579034411</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>32493.3601488201</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>37404.1469818018</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>34971.3402419007</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>34334.1602428189</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>40656.9012552127</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>242.034</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>402.705</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>545.8</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>787.648</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>801.377</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>1116.813</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1582.462</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>1379.75</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>969.444</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1102.175</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>1417.227</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>1587.496</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1328.998</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>1824.281</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>1660.801</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>1850.309</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>1464.824</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2094.203</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>2227.232</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2653.175</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2486.097</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2614.178</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2756.408</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>3619.127</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3054.713</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3431.323</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3502.325</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>146.15</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-42.9</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-54.42</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-67.5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-69.4</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-76.55</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-83.21</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-78.68</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-69.98</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-74.84</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-80.22</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-81.99</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-77.57</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-82.09</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-81.55</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-83.09</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-78.21</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-84.5</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-84.65</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>-84.79</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-81.48</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>-81.32</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>-81.7</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>-86.05</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>-83.09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>-84.12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>-83.99</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>4.92</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>23.321</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>8.559</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>9.305</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8.374</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>7.68</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.661</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.715</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.368</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>7.828</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>8.111</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>6.607</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>6.341</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6.698</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>7.267</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>6.386</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>5.467</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>6.175</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>6.843</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>5.281</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4.845</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5.505</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>4.046</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>4.487</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>3.793</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>4.954</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9153.4965955802</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>9874.10040182349</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>9410.98128028456</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10298.1579326109</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>11928.99667058</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>13534.3321489214</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>13235.7234957965</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>15172.9940814237</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>15354.3387812359</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>17570.1407687541</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>17345.8910444984</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>21875.0713068763</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>24283.9206552757</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>22272.0118664632</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>21076.2368875923</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>23737.7749551508</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>28174.2959473185</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>26825.6588240526</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>28974.095016329</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>29362.0957802234</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>33395.4717531876</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>35845.8429836864</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>35754.7214164351</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>33536.9344950557</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>40968.4062327742</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>43244.664856072</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>37901.0601690403</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>595777610.942204</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>229958000.000042</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>248787999.99994</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>255992999.999925</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>245256000.00004</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>261889000.000089</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>265623000.000073</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>294184000.000031</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>291053000.000056</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>277329999.99991</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>280268000.000107</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>285844999.999891</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>298127000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>326732000.000006</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>306411999.99999</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>312940999.999984</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>319241000.000067</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>324538000.000132</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>341931000.000055</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>403663231.002174</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>460432475.107833</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>488384873.64935</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>504298959.841828</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>504926079.304224</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>516498636.369573</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>544935618.470873</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>560596539.605667</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>673379560.43965</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>329400000.00003</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>333635999.999947</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>336767999.999921</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>332075000.000028</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>345225000.00007</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>355881000.00006</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>367319000.000039</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>367088000.000056</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>357903999.999912</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>360534000.000107</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>367969999.999883</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>376504999.999984</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>381132000.000021</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>370781999.999988</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>392508000.000017</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>388349000.000082</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>402130000.000187</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>430305000.00005</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>450901395.665593</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>517424076.01036</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>543542830.199463</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>561712055.741051</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>563358062.936238</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>577669143.218786</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>609490883.155899</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>628396783.026773</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>259712601.670991</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>164909043.258945</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>159410174.705552</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>161030245.338828</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>153551997.600638</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>161546486.253844</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>157948772.376516</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>163533256.452512</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>164383293.253354</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>163199539.449619</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>156510730.441613</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>159412537.388463</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>170025356.549252</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>169090871.454267</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>166289674.047494</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>160725289.298676</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>157584245.87148</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>163038969.813329</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>177393139.019845</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>181060235.665746</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>212685437.046823</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>227104966.753389</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>237067134.453503</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>227769797.619859</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>237510308.376104</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>247554901.472383</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>254594913.046604</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>337325.926931636</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>159200.000000026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>162499.999999964</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>164699.999999938</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>162999.999999995</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>169300.000000019</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>173800.000000063</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>182200.000000004</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>182300.000000066</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>181600.000000049</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>180999.999999954</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>186299.999999961</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>192199.999999992</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>194800.000000026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>191400.000000053</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>199399.999999981</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>197099.999999994</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>204400.000000003</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>216399.999999997</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>226682.59593969</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>259513.946752724</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>273694.301769222</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>283918.979690789</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>283827.608869209</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>291704.79985723</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>308059.228142981</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>317322.536084126</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>300772.257343065</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>140900.000000024</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>146399.999999965</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>149299.999999943</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>146600.000000004</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>153600.000000026</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>157100.000000066</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>168800.000000009</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>167800.000000069</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>166800.000000051</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>165699.999999953</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>170999.999999952</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>177099.999999985</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>180500.000000024</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>178500.000000051</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>180999.999999983</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>180999.999999991</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>186400.000000002</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>195899.999999996</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>204805.342039276</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>233295.699057251</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>247784.517937457</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>256949.079818848</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>256540.909451853</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>263084.724811131</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>277633.769173426</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>285439.619335998</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>673379560.43965</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>329400000.00003</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>333635999.999947</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>336767999.999921</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>332075000.000028</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>345225000.00007</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>355881000.00006</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>367319000.000039</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>367088000.000056</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>357903999.999912</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>360534000.000107</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>367969999.999883</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>376504999.999984</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>381132000.000021</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>370781999.999988</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>392508000.000017</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>388349000.000082</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>402130000.000187</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>430305000.00005</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>450901395.665593</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>517424076.01036</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>543542830.199463</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>561712055.741051</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>563358062.936238</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>577669143.218786</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>609490883.155899</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>628396783.026773</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>595777610.942204</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>229958000.000042</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>248787999.99994</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>255992999.999925</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>245256000.00004</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>261889000.000089</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>265623000.000073</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>294184000.000031</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>291053000.000056</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>277329999.99991</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>280268000.000107</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>285844999.999891</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>298127000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>326732000.000006</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>306411999.99999</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>312940999.999984</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>319241000.000067</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>324538000.000132</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>341931000.000055</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>403663231.002174</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>460432475.107833</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>488384873.64935</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>504298959.841828</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>504926079.304224</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>516498636.369573</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>544935618.470873</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>560596539.605667</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>36665.8352145377</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>39795.1864251302</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>42270.1756421258</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>46378.3697045147</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>55868.5933498895</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>67673.7844039663</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>70324.1500000365</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>71416.3385521332</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>73513.0528413193</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>83072.6597441611</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>92870.4307264679</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>110106.080094352</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>123119.2579273</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>127422.024626144</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>114464.033980091</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>132998.053239989</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>122579.004609625</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>150414.910317923</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>163951.909265426</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>193611.481422264</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>209303.006692797</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>220233.630640894</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>231173.429174819</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>239869.715182347</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>254279.197215001</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>267450.058805664</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>276644.440872672</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>11376.9877159211</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>11459.5728223519</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>12232.9386404125</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>12124.0824405057</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>14021.9025397447</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>15103.2445010557</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>16309.3021318069</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>15894.7805435406</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17146.4912025201</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>17116.6484510259</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>19994.5708848269</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>20141.8570878332</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>21901.04945079</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>24963.5052401376</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>24733.8933727091</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>26191.3190380865</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25446.2209697561</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>28048.0309852233</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>28851.0538556511</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>32532.2083531551</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>31343.8984585258</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>32357.3698222489</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>34915.2980937016</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>41160.2168813171</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>38037.7651639587</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>37953.1377351808</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>45456.6039711084</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
